--- a/output/pdf_financials_xlsx/THNC.xlsx
+++ b/output/pdf_financials_xlsx/THNC.xlsx
@@ -3511,22 +3511,22 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.44763</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.538826</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.521952</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.433</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.426</v>
       </c>
     </row>
     <row r="125">
@@ -3536,22 +3536,22 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.44763</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.538826</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.521952</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.433</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.426</v>
       </c>
     </row>
     <row r="126">
@@ -6486,7 +6486,11 @@
           <t>Operating lease payments</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -8042,7 +8046,11 @@
           <t>Operating lease payments 11</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E95" s="5" t="n">
         <v>-0.44763</v>
       </c>

--- a/output/pdf_financials_xlsx/THNC.xlsx
+++ b/output/pdf_financials_xlsx/THNC.xlsx
@@ -3220,10 +3220,10 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -6350,7 +6350,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -7070,7 +7074,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -7606,7 +7614,11 @@
           <t>Loss on disposal of property and equipment 9, 11</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/THNC.xlsx
+++ b/output/pdf_financials_xlsx/THNC.xlsx
@@ -1405,22 +1405,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.024034</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.111172</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.407816</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>1.368</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.239</v>
       </c>
     </row>
     <row r="41">
@@ -1430,22 +1430,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0.806687</v>
+        <v>0.830721</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1.392391</v>
+        <v>1.503563</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>2.712671</v>
+        <v>3.120487</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>4.262</v>
+        <v>5.63</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>4.585</v>
+        <v>5.335</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>5.209</v>
+        <v>5.448</v>
       </c>
     </row>
     <row r="42">
@@ -1605,22 +1605,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.488097</v>
+        <v>1.464063</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.92925</v>
+        <v>2.818078</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.119751</v>
+        <v>1.711935</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.272</v>
+        <v>2.904</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.928</v>
+        <v>3.178</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.735</v>
+        <v>3.496</v>
       </c>
     </row>
     <row r="49">
@@ -2017,16 +2017,16 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.369446</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>1.337753</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.405233</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.457161</v>
       </c>
       <c r="F64" s="3" t="n">
         <v>0</v>
@@ -2092,22 +2092,22 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.32726</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>1.145717</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>2.975664</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>1.739</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="68">
@@ -2167,22 +2167,22 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.492611</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.515348</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.443928</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.555</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.342</v>
       </c>
     </row>
     <row r="71">
@@ -2192,22 +2192,22 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.492611</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.515348</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.443928</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>0.555</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>0.342</v>
       </c>
     </row>
     <row r="72">
@@ -2292,22 +2292,22 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.492611</v>
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.515348</v>
+        <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.443928</v>
+        <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.555</v>
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.906</v>
+        <v>0.538</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.342</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2416,35 +2416,23 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.09278483139379821</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.004237582796098639</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0.005053339880215282</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.006773248718574567</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.008847429917776602</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.00790623482904501</v>
       </c>
     </row>
     <row r="81">
@@ -4394,7 +4382,11 @@
           <t>Lease liabilities (Note 9)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -5368,7 +5360,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>0.492611</v>
       </c>
@@ -5780,7 +5776,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
